--- a/outputs/54513.xlsx
+++ b/outputs/54513.xlsx
@@ -246,78 +246,72 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="35">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="19" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="2" xfId="17" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -325,55 +319,55 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="2" xfId="19" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="2" xfId="17" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="17" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -381,23 +375,19 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="9" fillId="0" borderId="2" xfId="19" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="2" xfId="17" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="17" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -653,63 +643,63 @@
   <dimension ref="B3:N19"/>
   <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="15.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="11.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="11.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="2.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="12.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="11.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="12.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="11.5"/>
   </cols>
   <sheetData>
-    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="1" t="s">
+    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B3" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="F3" s="3" t="n">
+      <c r="F3" s="4" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="4" t="n">
+    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B4" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="C4" s="5" t="n">
+      <c r="C4" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="D4" s="6"/>
-      <c r="E4" s="3" t="n">
+      <c r="D4" s="7"/>
+      <c r="E4" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="F4" s="7" t="n">
+      <c r="F4" s="8" t="n">
         <v>0.5</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="4" t="n">
+    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="5" t="n">
         <v>84</v>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C5" s="6" t="n">
         <v>0.55</v>
       </c>
-      <c r="D5" s="6"/>
-      <c r="E5" s="3" t="n">
+      <c r="D5" s="7"/>
+      <c r="E5" s="4" t="n">
         <v>84</v>
       </c>
       <c r="F5" s="8" t="n">
         <v>0.55</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
       <c r="D6" s="9"/>
@@ -734,7 +724,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="14"/>
       <c r="C8" s="15" t="n">
         <v>34.99</v>
@@ -747,18 +737,18 @@
         <v>0.55</v>
       </c>
       <c r="F8" s="18" t="n">
-        <f aca="false">C8*(1-E8)</f>
+        <f aca="false">C8*(1-C5)</f>
         <v>15.7455</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="19"/>
       <c r="C9" s="19"/>
       <c r="D9" s="19"/>
       <c r="E9" s="19"/>
       <c r="F9" s="19"/>
     </row>
-    <row r="10" s="20" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" s="20" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G10" s="21" t="s">
         <v>8</v>
       </c>
@@ -811,7 +801,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="12" s="20" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" s="20" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="20" t="n">
         <v>1</v>
       </c>
@@ -862,7 +852,7 @@
         <v>0.583333333333333</v>
       </c>
     </row>
-    <row r="13" s="20" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" s="20" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="20" t="n">
         <v>2</v>
       </c>
@@ -913,7 +903,7 @@
         <v>0.8625</v>
       </c>
     </row>
-    <row r="14" s="20" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" s="20" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="20" t="n">
         <v>3</v>
       </c>
@@ -964,7 +954,7 @@
         <v>1.14791666666667</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="26"/>
       <c r="C15" s="26"/>
       <c r="D15" s="26"/>
@@ -1015,14 +1005,14 @@
       <c r="G17" s="33" t="n">
         <v>75</v>
       </c>
-      <c r="H17" s="34" t="n">
+      <c r="H17" s="32" t="n">
         <f aca="false">IF(F17="","",(F17+G17))</f>
         <v>131</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="28"/>
-      <c r="C18" s="35" t="n">
+      <c r="C18" s="34" t="n">
         <v>2</v>
       </c>
       <c r="D18" s="30" t="n">
@@ -1039,14 +1029,14 @@
       <c r="G18" s="33" t="n">
         <v>75</v>
       </c>
-      <c r="H18" s="34" t="n">
+      <c r="H18" s="32" t="n">
         <f aca="false">IF(F18="","",(F18+G18))</f>
         <v>157.8</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="28"/>
-      <c r="C19" s="35" t="n">
+      <c r="C19" s="34" t="n">
         <v>3</v>
       </c>
       <c r="D19" s="30" t="n">
@@ -1063,7 +1053,7 @@
       <c r="G19" s="33" t="n">
         <v>75</v>
       </c>
-      <c r="H19" s="34" t="n">
+      <c r="H19" s="32" t="n">
         <f aca="false">IF(F19="","",(F19+G19))</f>
         <v>185.2</v>
       </c>

--- a/outputs/54513.xlsx
+++ b/outputs/54513.xlsx
@@ -246,11 +246,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="37">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -287,11 +293,15 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="19" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -311,7 +321,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="2" xfId="17" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -319,19 +329,19 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="2" xfId="19" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="2" xfId="17" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -347,11 +357,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -367,7 +377,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="17" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -375,19 +385,23 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="170" fontId="9" fillId="0" borderId="2" xfId="19" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="2" xfId="17" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="17" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -652,7 +666,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="11.5"/>
   </cols>
   <sheetData>
-    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="2" t="s">
         <v>0</v>
       </c>
@@ -669,7 +683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="5" t="n">
         <v>12</v>
       </c>
@@ -684,7 +698,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="5" t="n">
         <v>84</v>
       </c>
@@ -695,365 +709,365 @@
       <c r="E5" s="4" t="n">
         <v>84</v>
       </c>
-      <c r="F5" s="8" t="n">
+      <c r="F5" s="9" t="n">
         <v>0.55</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="J6" s="10"/>
+    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="10"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="J6" s="11"/>
     </row>
     <row r="7" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="E7" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="F7" s="13" t="s">
+      <c r="F7" s="14" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="14"/>
-      <c r="C8" s="15" t="n">
+    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="15"/>
+      <c r="C8" s="16" t="n">
         <v>34.99</v>
       </c>
-      <c r="D8" s="16" t="n">
+      <c r="D8" s="17" t="n">
         <v>96</v>
       </c>
-      <c r="E8" s="17" t="n">
+      <c r="E8" s="18" t="n">
         <f aca="false">VLOOKUP(D8,$B$4:$C$5,2,TRUE())</f>
         <v>0.55</v>
       </c>
-      <c r="F8" s="18" t="n">
+      <c r="F8" s="19" t="n">
         <f aca="false">C8*(1-C5)</f>
         <v>15.7455</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="19"/>
-      <c r="C9" s="19"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="19"/>
-    </row>
-    <row r="10" s="20" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G10" s="21" t="s">
+    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="20"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+    </row>
+    <row r="10" s="21" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G10" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="H10" s="21"/>
-      <c r="I10" s="21"/>
-      <c r="J10" s="21"/>
-      <c r="K10" s="21"/>
-      <c r="L10" s="21"/>
-      <c r="M10" s="21"/>
-      <c r="N10" s="21"/>
-    </row>
-    <row r="11" s="20" customFormat="true" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="22" t="s">
+      <c r="H10" s="22"/>
+      <c r="I10" s="22"/>
+      <c r="J10" s="22"/>
+      <c r="K10" s="22"/>
+      <c r="L10" s="22"/>
+      <c r="M10" s="22"/>
+      <c r="N10" s="22"/>
+    </row>
+    <row r="11" s="21" customFormat="true" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="22" t="s">
+      <c r="C11" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="22" t="s">
+      <c r="D11" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="E11" s="23" t="s">
+      <c r="E11" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="F11" s="22" t="s">
+      <c r="F11" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="G11" s="23" t="n">
+      <c r="G11" s="24" t="n">
         <v>12</v>
       </c>
-      <c r="H11" s="23" t="n">
+      <c r="H11" s="24" t="n">
         <v>24</v>
       </c>
-      <c r="I11" s="23" t="n">
+      <c r="I11" s="24" t="n">
         <v>36</v>
       </c>
-      <c r="J11" s="23" t="n">
+      <c r="J11" s="24" t="n">
         <v>48</v>
       </c>
-      <c r="K11" s="23" t="n">
+      <c r="K11" s="24" t="n">
         <v>60</v>
       </c>
-      <c r="L11" s="23" t="n">
+      <c r="L11" s="24" t="n">
         <v>72</v>
       </c>
-      <c r="M11" s="23" t="n">
+      <c r="M11" s="24" t="n">
         <v>84</v>
       </c>
-      <c r="N11" s="23" t="n">
+      <c r="N11" s="24" t="n">
         <v>96</v>
       </c>
     </row>
-    <row r="12" s="20" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="20" t="n">
+    <row r="12" s="21" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="C12" s="24" t="n">
+      <c r="C12" s="25" t="n">
         <v>0.5</v>
       </c>
-      <c r="D12" s="24" t="n">
+      <c r="D12" s="25" t="n">
         <f aca="false">12*C12</f>
         <v>6</v>
       </c>
-      <c r="E12" s="25" t="n">
+      <c r="E12" s="26" t="n">
         <v>50</v>
       </c>
-      <c r="F12" s="24" t="n">
+      <c r="F12" s="25" t="n">
         <f aca="false">E12+D12</f>
         <v>56</v>
       </c>
-      <c r="G12" s="24" t="n">
+      <c r="G12" s="25" t="n">
         <f aca="false">F12/$G$11</f>
         <v>4.66666666666667</v>
       </c>
-      <c r="H12" s="24" t="n">
+      <c r="H12" s="25" t="n">
         <f aca="false">F12/$H$11</f>
         <v>2.33333333333333</v>
       </c>
-      <c r="I12" s="24" t="n">
+      <c r="I12" s="25" t="n">
         <f aca="false">F12/$I$11</f>
         <v>1.55555555555556</v>
       </c>
-      <c r="J12" s="24" t="n">
+      <c r="J12" s="25" t="n">
         <f aca="false">F12/$J$11</f>
         <v>1.16666666666667</v>
       </c>
-      <c r="K12" s="24" t="n">
+      <c r="K12" s="25" t="n">
         <f aca="false">F12/$K$11</f>
         <v>0.933333333333333</v>
       </c>
-      <c r="L12" s="24" t="n">
+      <c r="L12" s="25" t="n">
         <f aca="false">F12/$L$11</f>
         <v>0.777777777777778</v>
       </c>
-      <c r="M12" s="24" t="n">
+      <c r="M12" s="25" t="n">
         <f aca="false">F12/$M$11</f>
         <v>0.666666666666667</v>
       </c>
-      <c r="N12" s="24" t="n">
+      <c r="N12" s="25" t="n">
         <f aca="false">F12/$N$11</f>
         <v>0.583333333333333</v>
       </c>
     </row>
-    <row r="13" s="20" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="20" t="n">
+    <row r="13" s="21" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="C13" s="24" t="n">
+      <c r="C13" s="25" t="n">
         <v>0.65</v>
       </c>
-      <c r="D13" s="24" t="n">
+      <c r="D13" s="25" t="n">
         <f aca="false">12*C13</f>
         <v>7.8</v>
       </c>
-      <c r="E13" s="25" t="n">
+      <c r="E13" s="26" t="n">
         <v>75</v>
       </c>
-      <c r="F13" s="24" t="n">
+      <c r="F13" s="25" t="n">
         <f aca="false">E13+D13</f>
         <v>82.8</v>
       </c>
-      <c r="G13" s="24" t="n">
+      <c r="G13" s="25" t="n">
         <f aca="false">F13/$G$11</f>
         <v>6.9</v>
       </c>
-      <c r="H13" s="24" t="n">
+      <c r="H13" s="25" t="n">
         <f aca="false">F13/$H$11</f>
         <v>3.45</v>
       </c>
-      <c r="I13" s="24" t="n">
+      <c r="I13" s="25" t="n">
         <f aca="false">F13/$I$11</f>
         <v>2.3</v>
       </c>
-      <c r="J13" s="24" t="n">
+      <c r="J13" s="25" t="n">
         <f aca="false">F13/$J$11</f>
         <v>1.725</v>
       </c>
-      <c r="K13" s="24" t="n">
+      <c r="K13" s="25" t="n">
         <f aca="false">F13/$K$11</f>
         <v>1.38</v>
       </c>
-      <c r="L13" s="24" t="n">
+      <c r="L13" s="25" t="n">
         <f aca="false">F13/$L$11</f>
         <v>1.15</v>
       </c>
-      <c r="M13" s="24" t="n">
+      <c r="M13" s="25" t="n">
         <f aca="false">F13/$M$11</f>
         <v>0.985714285714286</v>
       </c>
-      <c r="N13" s="24" t="n">
+      <c r="N13" s="25" t="n">
         <f aca="false">F13/$N$11</f>
         <v>0.8625</v>
       </c>
     </row>
-    <row r="14" s="20" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="20" t="n">
+    <row r="14" s="21" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="C14" s="24" t="n">
+      <c r="C14" s="25" t="n">
         <v>0.85</v>
       </c>
-      <c r="D14" s="24" t="n">
+      <c r="D14" s="25" t="n">
         <f aca="false">12*C14</f>
         <v>10.2</v>
       </c>
-      <c r="E14" s="20" t="n">
+      <c r="E14" s="21" t="n">
         <v>100</v>
       </c>
-      <c r="F14" s="24" t="n">
+      <c r="F14" s="25" t="n">
         <f aca="false">E14+D14</f>
         <v>110.2</v>
       </c>
-      <c r="G14" s="24" t="n">
+      <c r="G14" s="25" t="n">
         <f aca="false">F14/$G$11</f>
         <v>9.18333333333333</v>
       </c>
-      <c r="H14" s="24" t="n">
+      <c r="H14" s="25" t="n">
         <f aca="false">F14/$H$11</f>
         <v>4.59166666666667</v>
       </c>
-      <c r="I14" s="24" t="n">
+      <c r="I14" s="25" t="n">
         <f aca="false">F14/$I$11</f>
         <v>3.06111111111111</v>
       </c>
-      <c r="J14" s="24" t="n">
+      <c r="J14" s="25" t="n">
         <f aca="false">F14/$J$11</f>
         <v>2.29583333333333</v>
       </c>
-      <c r="K14" s="24" t="n">
+      <c r="K14" s="25" t="n">
         <f aca="false">F14/$K$11</f>
         <v>1.83666666666667</v>
       </c>
-      <c r="L14" s="24" t="n">
+      <c r="L14" s="25" t="n">
         <f aca="false">F14/$L$11</f>
         <v>1.53055555555556</v>
       </c>
-      <c r="M14" s="24" t="n">
+      <c r="M14" s="25" t="n">
         <f aca="false">F14/$M$11</f>
         <v>1.31190476190476</v>
       </c>
-      <c r="N14" s="24" t="n">
+      <c r="N14" s="25" t="n">
         <f aca="false">F14/$N$11</f>
         <v>1.14791666666667</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="26"/>
-      <c r="C15" s="26"/>
-      <c r="D15" s="26"/>
-      <c r="E15" s="26"/>
-      <c r="F15" s="26"/>
+    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="27"/>
+      <c r="C15" s="27"/>
+      <c r="D15" s="27"/>
+      <c r="E15" s="27"/>
+      <c r="F15" s="27"/>
     </row>
     <row r="16" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="27" t="s">
+      <c r="B16" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="C16" s="27" t="s">
+      <c r="C16" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="E16" s="12" t="s">
+      <c r="E16" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="F16" s="12" t="s">
+      <c r="F16" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="G16" s="12" t="s">
+      <c r="G16" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="H16" s="27" t="s">
+      <c r="H16" s="28" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="28" t="s">
+      <c r="B17" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="29" t="n">
+      <c r="C17" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="30" t="n">
+      <c r="D17" s="31" t="n">
         <v>48</v>
       </c>
-      <c r="E17" s="31" t="n">
+      <c r="E17" s="32" t="n">
         <f aca="false">IF(D17="","",(VLOOKUP(C17,$B$12:$N$14,MATCH(D17,$B$11:$N$11),)))</f>
         <v>1.16666666666667</v>
       </c>
-      <c r="F17" s="32" t="n">
+      <c r="F17" s="33" t="n">
         <f aca="false">IF(D17="","",(D17*E17))</f>
         <v>56</v>
       </c>
-      <c r="G17" s="33" t="n">
+      <c r="G17" s="34" t="n">
         <v>75</v>
       </c>
-      <c r="H17" s="32" t="n">
+      <c r="H17" s="35" t="n">
         <f aca="false">IF(F17="","",(F17+G17))</f>
         <v>131</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="28"/>
-      <c r="C18" s="34" t="n">
+    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="29"/>
+      <c r="C18" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="D18" s="30" t="n">
+      <c r="D18" s="31" t="n">
         <v>48</v>
       </c>
-      <c r="E18" s="31" t="n">
+      <c r="E18" s="32" t="n">
         <f aca="false">IF(D18="","",(VLOOKUP(C18,$B$12:$N$14,MATCH(D18,$B$11:$N$11),)))</f>
         <v>1.725</v>
       </c>
-      <c r="F18" s="32" t="n">
+      <c r="F18" s="33" t="n">
         <f aca="false">IF(D18="","",(D18*E18))</f>
         <v>82.8</v>
       </c>
-      <c r="G18" s="33" t="n">
+      <c r="G18" s="34" t="n">
         <v>75</v>
       </c>
-      <c r="H18" s="32" t="n">
+      <c r="H18" s="35" t="n">
         <f aca="false">IF(F18="","",(F18+G18))</f>
         <v>157.8</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="28"/>
-      <c r="C19" s="34" t="n">
+    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="29"/>
+      <c r="C19" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="D19" s="30" t="n">
+      <c r="D19" s="31" t="n">
         <v>48</v>
       </c>
-      <c r="E19" s="31" t="n">
+      <c r="E19" s="32" t="n">
         <f aca="false">IF(D19="","",(VLOOKUP(C19,$B$12:$N$14,MATCH(D19,$B$11:$N$11),)))</f>
         <v>2.29583333333333</v>
       </c>
-      <c r="F19" s="32" t="n">
+      <c r="F19" s="33" t="n">
         <f aca="false">IF(D19="","",(D19*E19))</f>
         <v>110.2</v>
       </c>
-      <c r="G19" s="33" t="n">
+      <c r="G19" s="34" t="n">
         <v>75</v>
       </c>
-      <c r="H19" s="32" t="n">
+      <c r="H19" s="35" t="n">
         <f aca="false">IF(F19="","",(F19+G19))</f>
         <v>185.2</v>
       </c>
